--- a/reports/devops-juniors-israel-2026-W34.xlsx
+++ b/reports/devops-juniors-israel-2026-W34.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17T07:12:21</t>
+    <t xml:space="preserve">2026-08-18T06:59:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -178,859 +181,838 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">software development student</t>
+    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-at-radware-4452112960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4455175909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moovit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-sqlink-group-4452238645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onyx Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-onyx-security-4454296694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TechAviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-techaviv-4452298224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-candex-4454009475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-comblack-4454021597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4451634323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator- Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-microsoft-at-abra-4451111887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (36859)</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (37347)</t>
   </si>
   <si>
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-36859-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4453698899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Student, AWS Annapurna Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-development-student-aws-annapurna-labs-at-amazon-web-services-aws-4443046179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technical-support-at-fiverr-4449741839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Technologies, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravity Forms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-gravity-forms-4450978605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior NOC Engineer | Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-noc-engineer-student-position-at-log-on-software-4450132712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-37347-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455275814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455189813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1049,6 +1031,9 @@
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1188,7 +1173,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -1196,7 +1181,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1204,7 +1189,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1212,7 +1197,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10">
@@ -1294,7 +1279,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -1302,7 +1287,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1310,7 +1295,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1318,32 +1303,40 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>47</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
         <v>10</v>
       </c>
     </row>
@@ -1368,34 +1361,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -1403,13 +1396,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>26</v>
@@ -1418,16 +1411,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1435,13 +1428,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>28</v>
@@ -1450,16 +1443,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -1467,31 +1460,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1499,13 +1492,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1514,16 +1507,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1531,13 +1524,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1546,16 +1539,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1563,13 +1556,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1578,16 +1571,16 @@
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1595,13 +1588,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
@@ -1610,16 +1603,16 @@
         <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -1627,13 +1620,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1642,16 +1635,16 @@
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1659,13 +1652,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1674,16 +1667,16 @@
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -1691,13 +1684,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1706,16 +1699,16 @@
         <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -1723,13 +1716,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1738,16 +1731,16 @@
         <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -1755,13 +1748,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1770,16 +1763,16 @@
         <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1787,31 +1780,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1819,25 +1812,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>114</v>
@@ -1854,28 +1847,28 @@
         <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
+        <v>52</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -1883,13 +1876,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -1898,16 +1891,16 @@
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1915,13 +1908,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1930,16 +1923,16 @@
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
@@ -1947,13 +1940,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -1962,16 +1955,16 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20">
@@ -1979,13 +1972,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
@@ -1997,7 +1990,7 @@
         <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>139</v>
@@ -2011,13 +2004,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
@@ -2026,16 +2019,16 @@
         <v>48</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22">
@@ -2043,31 +2036,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23">
@@ -2075,31 +2068,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
@@ -2107,31 +2100,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>158</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
@@ -2139,31 +2132,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26">
@@ -2171,31 +2164,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2234,7 +2227,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2248,48 +2241,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>26</v>
@@ -2298,33 +2291,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>28</v>
@@ -2333,68 +2326,68 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2403,33 +2396,33 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2438,33 +2431,33 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2473,33 +2466,33 @@
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
@@ -2508,33 +2501,33 @@
         <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2543,33 +2536,33 @@
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
@@ -2578,33 +2571,33 @@
         <v>92</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2613,33 +2606,33 @@
         <v>88</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="K11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2648,33 +2641,33 @@
         <v>88</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>27</v>
@@ -2683,83 +2676,83 @@
         <v>83</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="K14" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>114</v>
@@ -2768,7 +2761,7 @@
         <v>115</v>
       </c>
       <c r="K15" s="3">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2776,45 +2769,45 @@
         <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
+        <v>52</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K16" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -2823,33 +2816,33 @@
         <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2858,33 +2851,33 @@
         <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K18" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -2893,33 +2886,33 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K19" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
@@ -2931,10 +2924,10 @@
         <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>139</v>
@@ -2943,18 +2936,18 @@
         <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
@@ -2963,628 +2956,628 @@
         <v>48</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K21" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K22" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="K23" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="K24" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="K25" s="3">
-        <v>3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
+        <v>27</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="3">
         <v>28</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K27" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="K28" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K31" s="3">
         <v>30</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K31" s="3">
-        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>198</v>
+        <v>60</v>
       </c>
       <c r="K32" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="K33" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K34" s="3">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="K35" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="K36" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K37" s="3">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>216</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="K38" s="3">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>161</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3593,33 +3586,33 @@
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="K39" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3628,103 +3621,103 @@
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>140</v>
       </c>
       <c r="K40" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>92</v>
+        <v>240</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="K41" s="3">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
         <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="K42" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3733,264 +3726,264 @@
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="K43" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>255</v>
+        <v>65</v>
       </c>
       <c r="K44" s="3">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="J45" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="K45" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="3">
-        <v>12</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K46" s="3">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="3">
-        <v>12</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="G48" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>10</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K48" s="3">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="K49" s="3">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="K50" s="3">
         <v>0</v>
@@ -3998,83 +3991,83 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>101</v>
+        <v>281</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>102</v>
+        <v>282</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K51" s="3">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K52" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4083,33 +4076,33 @@
         <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4118,33 +4111,33 @@
         <v>3</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K54" s="3">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>298</v>
+        <v>93</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4153,129 +4146,59 @@
         <v>3</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="K55" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>289</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="K56" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="K57" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K58" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K58"/>
+  <autoFilter ref="A1:K56"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4332,8 +4255,6 @@
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4341,9 +4262,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4352,126 +4273,270 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>276</v>
+        <v>117</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>273</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="3">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>75</v>
+      <c r="E11" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4486,178 +4551,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B3" s="3">
         <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B5" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>323</v>
+        <v>241</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B11" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B14" s="3">
         <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B16" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4674,13 +4739,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2">
@@ -4688,10 +4753,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
@@ -4699,10 +4764,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
@@ -4710,10 +4775,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5">
@@ -4721,10 +4786,21 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>344</v>
+      <c r="C6" s="3" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4742,51 +4818,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W34.xlsx
+++ b/reports/devops-juniors-israel-2026-W34.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18T06:59:23</t>
+    <t xml:space="preserve">2026-08-19T07:00:31</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -214,114 +214,105 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4448158765</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-03</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455203355</t>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-17</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
-  </si>
-  <si>
     <t xml:space="preserve">Devops Student</t>
   </si>
   <si>
@@ -364,18 +355,6 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator &amp; IT</t>
   </si>
   <si>
@@ -484,6 +463,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4455175909</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
     <t xml:space="preserve">Moovit</t>
   </si>
   <si>
@@ -529,6 +523,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -547,16 +553,16 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
@@ -586,6 +592,36 @@
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
   </si>
   <si>
@@ -631,13 +667,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-sqlink-group-4452238645</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+    <t xml:space="preserve">23343 - IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
   </si>
   <si>
     <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
@@ -661,9 +706,6 @@
     <t xml:space="preserve">Harmonic</t>
   </si>
   <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
   </si>
   <si>
@@ -691,9 +733,6 @@
     <t xml:space="preserve">Help Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -760,13 +799,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
-    <t xml:space="preserve">TechAviv</t>
+    <t xml:space="preserve">Kaltura</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-techaviv-4452298224</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone Technologies, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
   </si>
   <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
@@ -817,6 +880,51 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
   </si>
   <si>
+    <t xml:space="preserve">Stratacom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-stratacom-4455254999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Support Specialist - 5661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-support-specialist-5661-at-entrypoint-4454248307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-reline-it-solutions-4452232857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -844,58 +952,46 @@
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Support Specialist</t>
@@ -949,9 +1045,6 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -961,6 +1054,15 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -970,21 +1072,15 @@
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -1003,16 +1099,10 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1173,7 +1263,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -1181,7 +1271,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1189,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1287,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10">
@@ -1279,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -1287,7 +1377,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1295,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1329,7 +1419,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
@@ -1524,13 +1614,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1539,16 +1629,16 @@
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1556,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1594,19 +1684,19 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -1626,7 +1716,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1635,16 +1725,16 @@
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1652,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>88</v>
@@ -1661,10 +1751,10 @@
         <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>90</v>
@@ -1676,7 +1766,7 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1684,13 +1774,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1699,16 +1789,16 @@
         <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1716,31 +1806,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1748,31 +1838,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1780,31 +1870,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1812,31 +1902,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -1844,31 +1934,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1876,31 +1966,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1908,31 +1998,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1940,13 +2030,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
@@ -1955,16 +2045,16 @@
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -1972,31 +2062,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -2004,31 +2094,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2036,31 +2126,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F22" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
@@ -2068,31 +2158,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2100,31 +2190,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -2132,31 +2222,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26">
@@ -2164,31 +2254,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2241,7 +2331,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2256,22 +2346,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2294,7 +2384,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2306,7 +2396,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2329,7 +2419,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2341,7 +2431,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -2364,7 +2454,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2376,7 +2466,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2399,7 +2489,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2411,18 +2501,18 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2431,33 +2521,33 @@
         <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2469,7 +2559,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2481,7 +2571,7 @@
         <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -2492,22 +2582,22 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -2516,7 +2606,7 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2527,7 +2617,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2536,27 +2626,27 @@
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>88</v>
@@ -2565,16 +2655,16 @@
         <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
@@ -2583,21 +2673,21 @@
         <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2606,278 +2696,278 @@
         <v>88</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="K13" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K15" s="3">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
@@ -2886,313 +2976,313 @@
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="K21" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E22" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="K22" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="K25" s="3">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>71</v>
       </c>
       <c r="K27" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3201,33 +3291,33 @@
         <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K28" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3236,103 +3326,103 @@
         <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>96</v>
+        <v>197</v>
       </c>
       <c r="K30" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>197</v>
+        <v>68</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>139</v>
       </c>
       <c r="K31" s="3">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
@@ -3341,33 +3431,33 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3376,33 +3466,33 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="K33" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3411,103 +3501,103 @@
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>212</v>
+        <v>60</v>
       </c>
       <c r="K34" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K35" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K36" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3516,33 +3606,33 @@
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="K37" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3551,33 +3641,33 @@
         <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="K38" s="3">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3586,33 +3676,33 @@
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>60</v>
+        <v>232</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3621,205 +3711,205 @@
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="K40" s="3">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>159</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>243</v>
+        <v>60</v>
       </c>
       <c r="K41" s="3">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>99</v>
+        <v>250</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>246</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K42" s="3">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="K44" s="3">
-        <v>86</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="K45" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>57</v>
@@ -3828,223 +3918,223 @@
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="K46" s="3">
-        <v>86</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>103</v>
+        <v>273</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>270</v>
+        <v>65</v>
       </c>
       <c r="K48" s="3">
-        <v>47</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>275</v>
+        <v>48</v>
       </c>
       <c r="K49" s="3">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>285</v>
+        <v>60</v>
       </c>
       <c r="K51" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
@@ -4053,112 +4143,112 @@
         <v>289</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="K52" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>292</v>
+        <v>180</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>298</v>
+        <v>71</v>
       </c>
       <c r="K54" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>93</v>
+        <v>298</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K55" s="3">
         <v>0</v>
@@ -4166,39 +4256,319 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="J56" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K56" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="B57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="G57" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K57" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K58" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K59" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K60" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K61" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K62" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E64" s="3">
         <v>0</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K56" s="3">
-        <v>20</v>
+      <c r="I64" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K64" s="3">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K56"/>
+  <autoFilter ref="A1:K64"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4255,6 +4625,14 @@
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
+    <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4262,9 +4640,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4285,10 +4663,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4296,171 +4674,171 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>125</v>
+        <v>283</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>203</v>
+        <v>286</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>233</v>
+        <v>291</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>25</v>
@@ -4469,63 +4847,17 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4535,8 +4867,6 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4551,178 +4881,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>283</v>
+        <v>320</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>241</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="B10" s="3">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="B11" s="3">
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="B13" s="3">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="B14" s="3">
         <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="B15" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -4742,10 +5072,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -4753,10 +5083,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3">
@@ -4764,10 +5094,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4">
@@ -4775,10 +5105,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
@@ -4789,7 +5119,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6">
@@ -4800,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -4821,13 +5151,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -4838,7 +5168,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4847,22 +5177,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W34.xlsx
+++ b/reports/devops-juniors-israel-2026-W34.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19T07:00:31</t>
+    <t xml:space="preserve">2026-08-20T07:00:57</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -163,6 +163,42 @@
     <t xml:space="preserve">2026-07-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -181,22 +217,16 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
     <t xml:space="preserve">Linux System Administrator</t>
@@ -295,274 +325,289 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Developer - SAP BTP - CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-developer-sap-btp-ccs-at-sap-4343365945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-logica-it-4452227142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator for Computing Qual (testing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-for-computing-qual-testing-at-applied-materials-israel-4449806027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4455175909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moovit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-moovit-4453119234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
   </si>
   <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
@@ -571,9 +616,6 @@
     <t xml:space="preserve">Nebius</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -592,36 +634,6 @@
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAT Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
   </si>
   <si>
@@ -637,36 +649,6 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
   </si>
   <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-sqlink-group-4452238645</t>
-  </si>
-  <si>
     <t xml:space="preserve">23343 - IT Support Specialist</t>
   </si>
   <si>
@@ -682,22 +664,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
+    <t xml:space="preserve">Finance Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
   </si>
   <si>
     <t xml:space="preserve">Lab Support Engineer</t>
@@ -751,27 +727,6 @@
     <t xml:space="preserve">2026-07-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Onyx Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-onyx-security-4454296694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-confidential-4444582152</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
   </si>
   <si>
@@ -799,322 +754,184 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Field Operations Technician (IT Support)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milestone Technologies, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-field-operations-technician-it-support-at-milestone-technologies-inc-4434855297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratacom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-stratacom-4455254999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; IT Support Specialist - 5661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-support-specialist-5661-at-entrypoint-4454248307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-reline-it-solutions-4452232857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givat Shmuel, Center District, Israel</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4448140764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (37347)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-37347-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4455275814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
@@ -1263,7 +1080,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -1279,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1287,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10">
@@ -1369,7 +1186,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1377,7 +1194,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1385,7 +1202,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1419,7 +1236,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1427,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1495,7 +1312,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1559,7 +1376,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1588,25 +1405,25 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1614,16 +1431,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
@@ -1638,7 +1455,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -1646,31 +1463,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1678,25 +1495,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -1716,25 +1533,25 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1742,31 +1559,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="3">
+        <v>92</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3">
-        <v>88</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1774,31 +1591,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="3">
-        <v>88</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1806,31 +1623,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>88</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3">
-        <v>83</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1838,31 +1655,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>83</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>80</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1873,28 +1690,28 @@
         <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1902,31 +1719,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -1934,31 +1751,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>51</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -1966,31 +1783,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>60</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="3">
-        <v>48</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -1998,31 +1815,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -2030,31 +1847,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
         <v>48</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
@@ -2062,31 +1879,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -2094,31 +1911,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>48</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3">
-        <v>44</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2126,31 +1943,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="3">
+        <v>47</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="3">
-        <v>41</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="23">
@@ -2158,31 +1975,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" s="3">
+        <v>47</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>37</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2190,31 +2007,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="3">
+        <v>41</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>30</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
@@ -2222,31 +2039,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3">
+        <v>39</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3">
-        <v>28</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -2254,31 +2071,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2317,7 +2134,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2331,7 +2148,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2346,22 +2163,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2375,7 +2192,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2384,7 +2201,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2396,7 +2213,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2419,7 +2236,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2431,7 +2248,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>78</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2445,7 +2262,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2454,7 +2271,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2466,7 +2283,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2477,45 +2294,45 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -2524,7 +2341,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2533,7 +2350,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -2541,63 +2358,63 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K7" s="3">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -2606,7 +2423,7 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2617,171 +2434,171 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>92</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K9" s="3">
-        <v>16</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3">
+        <v>92</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3">
-        <v>88</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K10" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3">
+        <v>92</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="3">
-        <v>88</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="K11" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>88</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3">
-        <v>83</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>83</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>80</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -2789,486 +2606,486 @@
         <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="K14" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K15" s="3">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3">
+        <v>70</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="K16" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>60</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="3">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="K17" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K18" s="3">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
         <v>48</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K20" s="3">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>48</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="3">
-        <v>44</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K21" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3">
+        <v>47</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="3">
-        <v>41</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="3">
+        <v>47</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>37</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3">
+        <v>41</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>30</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="K24" s="3">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>39</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="3">
-        <v>28</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="K25" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="K26" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>28</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>24</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -3276,60 +3093,60 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K28" s="3">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>27</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>23</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
@@ -3338,1237 +3155,677 @@
         <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>102</v>
       </c>
       <c r="K29" s="3">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="K30" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="K31" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>23</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="K32" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="K33" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="K35" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="K36" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K37" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
         <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="K38" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
         <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K39" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
         <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="K40" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>159</v>
+        <v>237</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>245</v>
+        <v>88</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="K41" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="K42" s="3">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>256</v>
+        <v>75</v>
       </c>
       <c r="K43" s="3">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>95</v>
+        <v>253</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="K44" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>261</v>
+        <v>113</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>265</v>
+        <v>104</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="K46" s="3">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="K48" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K49" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K50" s="3">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>6</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K51" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>6</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>6</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>6</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>6</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K55" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="3">
-        <v>6</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K56" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="K57" s="3">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K58" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K59" s="3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="K60" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K61" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="K62" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="3">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K64" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K64"/>
+  <autoFilter ref="A1:K48"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4617,22 +3874,6 @@
     <hyperlink ref="I46" r:id="rId45"/>
     <hyperlink ref="I47" r:id="rId46"/>
     <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
-    <hyperlink ref="I50" r:id="rId49"/>
-    <hyperlink ref="I51" r:id="rId50"/>
-    <hyperlink ref="I52" r:id="rId51"/>
-    <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
-    <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4640,8 +3881,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4663,10 +3904,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4674,186 +3915,186 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>238</v>
+        <v>117</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>262</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>263</v>
+        <v>121</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>161</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>288</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>286</v>
+        <v>164</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>290</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>291</v>
+        <v>178</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>292</v>
+        <v>179</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>293</v>
+        <v>193</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>296</v>
+        <v>197</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>297</v>
+        <v>88</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>299</v>
+        <v>219</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4874,185 +4115,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>272</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>273</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>340</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>344</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="B6" s="3">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>345</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>283</v>
       </c>
       <c r="B7" s="3">
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>346</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>348</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>350</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>351</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>353</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>354</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>356</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>357</v>
+        <v>296</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>358</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>359</v>
+        <v>298</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>360</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>362</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -5072,10 +4313,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2">
@@ -5083,10 +4324,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -5094,10 +4335,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -5105,10 +4346,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -5119,7 +4360,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>368</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6">
@@ -5130,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -5151,13 +4392,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>372</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
@@ -5165,10 +4406,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5177,22 +4418,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W34.xlsx
+++ b/reports/devops-juniors-israel-2026-W34.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20T07:00:57</t>
+    <t xml:space="preserve">2026-08-21T07:02:30</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,12 +100,12 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -163,634 +163,580 @@
     <t xml:space="preserve">2026-07-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4455339838</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4440108780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOC Analyst Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-analyst-tier-1-at-log-on-software-4453436238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-yael-korentec-technologies-4456163934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-sqlink-group-4453416679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4454032601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Developer - SAP BTP - CCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-developer-sap-btp-ccs-at-sap-4343365945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23343 - IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualitest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/23343-it-support-specialist-at-qualitest-4447935579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+    <t xml:space="preserve">Stratacom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-stratacom-4455254999</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -820,6 +766,27 @@
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
   </si>
   <si>
@@ -841,36 +808,30 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -892,16 +853,22 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -916,12 +883,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -937,10 +898,10 @@
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1080,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -1088,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1096,7 +1057,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1104,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10">
@@ -1186,7 +1147,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1202,7 +1163,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1236,7 +1197,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
@@ -1344,7 +1305,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1376,7 +1337,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1408,7 +1369,7 @@
         <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1423,7 +1384,7 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -1431,13 +1392,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1455,7 +1416,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1463,13 +1424,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -1478,16 +1439,16 @@
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1495,13 +1456,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1533,19 +1494,19 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>85</v>
@@ -1565,7 +1526,7 @@
         <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1574,16 +1535,16 @@
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1591,31 +1552,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1623,31 +1584,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1655,19 +1616,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>106</v>
@@ -1679,7 +1640,7 @@
         <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1687,19 +1648,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>110</v>
@@ -1711,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1719,31 +1680,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1751,31 +1712,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1783,31 +1744,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1776,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1847,31 +1808,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -1879,31 +1840,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -1911,31 +1872,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1943,31 +1904,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1975,31 +1936,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24">
@@ -2007,31 +1968,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
@@ -2039,31 +2000,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -2071,31 +2032,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2148,7 +2109,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2163,22 +2124,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2201,7 +2162,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2213,7 +2174,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2227,7 +2188,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2236,7 +2197,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2248,7 +2209,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2262,7 +2223,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2271,7 +2232,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2283,7 +2244,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -2297,7 +2258,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2306,7 +2267,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2315,21 +2276,21 @@
         <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K5" s="3">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2341,7 +2302,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2350,21 +2311,21 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -2373,33 +2334,33 @@
         <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2411,7 +2372,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2423,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -2434,22 +2395,22 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>85</v>
@@ -2458,7 +2419,7 @@
         <v>86</v>
       </c>
       <c r="K9" s="3">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -2469,7 +2430,7 @@
         <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
@@ -2478,115 +2439,115 @@
         <v>92</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2595,33 +2556,33 @@
         <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K13" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2630,453 +2591,453 @@
         <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="K19" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K20" s="3">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>81</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K23" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K26" s="3">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
@@ -3085,33 +3046,33 @@
         <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
@@ -3120,115 +3081,115 @@
         <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="K28" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -3239,31 +3200,31 @@
         <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="K32" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3271,92 +3232,92 @@
         <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K33" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="K34" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
@@ -3365,10 +3326,10 @@
         <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K35" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -3376,34 +3337,34 @@
         <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>88</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>218</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3414,418 +3375,383 @@
         <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>224</v>
+        <v>76</v>
       </c>
       <c r="K37" s="3">
-        <v>14</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="K38" s="3">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>8</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="3">
-        <v>17</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="K39" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>17</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="K40" s="3">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="3">
-        <v>13</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="K41" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="K42" s="3">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>247</v>
+        <v>94</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>248</v>
+        <v>95</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="K43" s="3">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>54</v>
+        <v>249</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>113</v>
+        <v>251</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>104</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K46" s="3">
         <v>4</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="K46" s="3">
-        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E47" s="3">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>265</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>267</v>
+        <v>129</v>
       </c>
       <c r="K47" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K48" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K48"/>
+  <autoFilter ref="A1:K47"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3873,7 +3799,6 @@
     <hyperlink ref="I45" r:id="rId44"/>
     <hyperlink ref="I46" r:id="rId45"/>
     <hyperlink ref="I47" r:id="rId46"/>
-    <hyperlink ref="I48" r:id="rId47"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3881,11 +3806,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3904,10 +3829,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3915,199 +3840,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>117</v>
+        <v>227</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4115,185 +3968,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3">
         <v>32</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B3" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4313,10 +4166,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2">
@@ -4324,10 +4177,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
@@ -4338,7 +4191,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4">
@@ -4346,10 +4199,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
@@ -4360,7 +4213,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -4371,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4392,13 +4245,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
@@ -4409,7 +4262,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4418,22 +4271,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W34.xlsx
+++ b/reports/devops-juniors-israel-2026-W34.xlsx
@@ -5,16 +5,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
-    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
-    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
-    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
+    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
+    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="316">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21T07:02:30</t>
+    <t xml:space="preserve">2026-08-23T06:56:39</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,21 +90,21 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -163,55 +162,55 @@
     <t xml:space="preserve">2026-07-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
@@ -232,21 +231,6 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -406,385 +390,448 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4440108780</t>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-sqlink-group-4452238645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441086540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOC Analyst Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-analyst-tier-1-at-log-on-software-4453436238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; IT Support Specialist - 5661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-it-support-specialist-5661-at-entrypoint-4454248307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
   </si>
   <si>
     <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-yael-korentec-technologies-4456163934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-sqlink-group-4453416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratacom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-stratacom-4455254999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
   </si>
   <si>
     <t xml:space="preserve">Working Student, Legal (German)</t>
@@ -811,30 +858,39 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -847,10 +903,10 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Git</t>
@@ -859,22 +915,10 @@
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -889,19 +933,19 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1041,7 +1085,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -1049,7 +1093,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1057,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1065,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>629</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10">
@@ -1147,7 +1191,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1155,7 +1199,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1163,7 +1207,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1171,7 +1215,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1197,7 +1241,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1273,7 +1317,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1305,7 +1349,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1337,7 +1381,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1366,25 +1410,25 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -1401,7 +1445,7 @@
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
@@ -1433,7 +1477,7 @@
         <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
@@ -1462,19 +1506,19 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -1494,7 +1538,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1503,16 +1547,16 @@
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1520,31 +1564,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="3">
+        <v>83</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1552,31 +1596,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1584,31 +1628,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -1616,31 +1660,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>52</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>60</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -1654,25 +1698,25 @@
         <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1680,31 +1724,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1712,16 +1756,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
@@ -1750,25 +1794,25 @@
         <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1782,25 +1826,25 @@
         <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -1817,10 +1861,10 @@
         <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3">
         <v>28</v>
-      </c>
-      <c r="F19" s="3">
-        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>138</v>
@@ -1832,7 +1876,7 @@
         <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1840,31 +1884,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -1872,31 +1916,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
@@ -1904,31 +1948,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23">
@@ -1936,19 +1980,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>157</v>
@@ -1968,31 +2012,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25">
@@ -2000,31 +2044,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
@@ -2032,31 +2076,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2139,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2109,7 +2153,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2124,22 +2168,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2153,7 +2197,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2162,7 +2206,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2174,7 +2218,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2188,7 +2232,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2197,7 +2241,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2209,7 +2253,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -2223,7 +2267,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2232,7 +2276,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2244,7 +2288,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2255,31 +2299,31 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -2293,7 +2337,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
         <v>100</v>
@@ -2302,7 +2346,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2314,7 +2358,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2328,7 +2372,7 @@
         <v>57</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
         <v>100</v>
@@ -2337,7 +2381,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2349,7 +2393,7 @@
         <v>76</v>
       </c>
       <c r="K7" s="3">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -2360,22 +2404,22 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>80</v>
@@ -2384,7 +2428,7 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>70</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -2395,7 +2439,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2404,162 +2448,162 @@
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3">
+        <v>83</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="3">
         <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" s="3">
-        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K12" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K13" s="3">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2570,80 +2614,80 @@
         <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3">
-        <v>9</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
         <v>47</v>
@@ -2652,7 +2696,7 @@
         <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
@@ -2664,7 +2708,7 @@
         <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -2675,31 +2719,31 @@
         <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="K17" s="3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2710,31 +2754,31 @@
         <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -2748,16 +2792,16 @@
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
         <v>28</v>
-      </c>
-      <c r="E19" s="3">
-        <v>41</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2766,138 +2810,138 @@
         <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="K21" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="K22" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -2909,333 +2953,333 @@
         <v>159</v>
       </c>
       <c r="K23" s="3">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="K25" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K27" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="K28" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>187</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="K29" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>195</v>
+        <v>96</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>17</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3244,348 +3288,348 @@
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K33" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="K34" s="3">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="K35" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
         <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="K36" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="K37" s="3">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>233</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>232</v>
+        <v>95</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>238</v>
+        <v>124</v>
       </c>
       <c r="K41" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>235</v>
+        <v>96</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
         <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K42" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>27</v>
@@ -3594,164 +3638,199 @@
         <v>4</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="K43" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E44" s="3">
         <v>4</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="K44" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="K45" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>63</v>
+        <v>265</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3">
         <v>3</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="K46" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>259</v>
+        <v>68</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K47" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E48" s="3">
         <v>0</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K47" s="3">
-        <v>23</v>
+      <c r="I48" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K48" s="3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K47"/>
+  <autoFilter ref="A1:K48"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3799,173 +3878,12 @@
     <hyperlink ref="I45" r:id="rId44"/>
     <hyperlink ref="I46" r:id="rId45"/>
     <hyperlink ref="I47" r:id="rId46"/>
+    <hyperlink ref="I48" r:id="rId47"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="3">
-        <v>44</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G6"/>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-  </hyperlinks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3975,185 +3893,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -4166,10 +4084,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
@@ -4177,10 +4095,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
@@ -4188,10 +4106,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4">
@@ -4199,10 +4117,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -4210,10 +4128,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6">
@@ -4224,14 +4142,14 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4245,13 +4163,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
@@ -4262,7 +4180,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4271,22 +4189,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D4" s="3"/>
     </row>
